--- a/assets/SEFrule.xlsx
+++ b/assets/SEFrule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trambert/projects/Bidding/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96F01F11-0564-EC49-81A0-ED3E958208D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0035620-C35A-484A-BDF0-3477F2563E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{C67589D8-C51A-194F-8A92-BFA7BFE68D55}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="38400" windowHeight="21000" xr2:uid="{C67589D8-C51A-194F-8A92-BFA7BFE68D55}"/>
   </bookViews>
   <sheets>
     <sheet name="rules" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2728" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2684" uniqueCount="478">
   <si>
     <t>Enchère</t>
   </si>
@@ -1369,36 +1369,15 @@
     <t>2T - 2SA - 3K -</t>
   </si>
   <si>
-    <t>CHELEM</t>
-  </si>
-  <si>
     <t>control</t>
   </si>
   <si>
-    <t>4E -</t>
-  </si>
-  <si>
-    <t>blackwood</t>
-  </si>
-  <si>
     <t>C,nn,pp or ""</t>
   </si>
   <si>
     <t>C: couleur de fit, nn: HLD mini du joueur 1, pp: HLD mini du joueur 3.</t>
   </si>
   <si>
-    <t>4SA - 5E -</t>
-  </si>
-  <si>
-    <t>- -</t>
-  </si>
-  <si>
-    <t>6E -</t>
-  </si>
-  <si>
-    <t>7E -</t>
-  </si>
-  <si>
     <t>2T - 2E - 3m</t>
   </si>
   <si>
@@ -1447,9 +1426,6 @@
     <t>1SA - 3K -</t>
   </si>
   <si>
-    <t>1SA - 3M -</t>
-  </si>
-  <si>
     <t>K2</t>
   </si>
   <si>
@@ -1471,9 +1447,6 @@
     <t>none</t>
   </si>
   <si>
-    <t>3E -</t>
-  </si>
-  <si>
     <t>Id de l'enchère dans SEFsense</t>
   </si>
   <si>
@@ -1496,6 +1469,9 @@
   </si>
   <si>
     <t>12-15HLD</t>
+  </si>
+  <si>
+    <t>=0</t>
   </si>
 </sst>
 </file>
@@ -1613,7 +1589,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1680,6 +1656,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2015,7 +1994,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E999B0E-BCB1-0548-9F4F-0A962A7A4ADD}">
-  <dimension ref="A1:Y392"/>
+  <dimension ref="A1:Y383"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="10" customWidth="1"/>
@@ -2049,7 +2028,7 @@
         <v>350</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="D1" s="12" t="s">
         <v>168</v>
@@ -2112,10 +2091,10 @@
         <v>324</v>
       </c>
       <c r="X1" s="12" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="Y1" s="12" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
     </row>
     <row r="2" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4745,7 +4724,7 @@
       </c>
       <c r="C60" s="20"/>
       <c r="D60" s="21" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="E60" s="20"/>
       <c r="F60" s="20"/>
@@ -14588,7 +14567,7 @@
         <v>142</v>
       </c>
       <c r="Y282" s="1" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="283" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -14629,7 +14608,7 @@
         <v>33</v>
       </c>
       <c r="Y283" s="1" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="284" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -14670,7 +14649,7 @@
         <v>142</v>
       </c>
       <c r="Y284" s="1" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="285" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -14711,7 +14690,7 @@
         <v>68</v>
       </c>
       <c r="Y285" s="1" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="286" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -14752,7 +14731,7 @@
         <v>142</v>
       </c>
       <c r="Y286" s="1" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="287" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -14793,7 +14772,7 @@
         <v>72</v>
       </c>
       <c r="Y287" s="1" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="288" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -15010,7 +14989,7 @@
         <v>142</v>
       </c>
       <c r="Y292" s="20" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="293" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -15205,7 +15184,7 @@
         <v>386</v>
       </c>
       <c r="C297" s="20" t="s">
-        <v>386</v>
+        <v>467</v>
       </c>
       <c r="D297" s="20" t="s">
         <v>367</v>
@@ -15252,7 +15231,7 @@
         <v>386</v>
       </c>
       <c r="C298" s="20" t="s">
-        <v>386</v>
+        <v>467</v>
       </c>
       <c r="D298" s="20" t="s">
         <v>367</v>
@@ -15302,7 +15281,7 @@
         <v>393</v>
       </c>
       <c r="D299" s="20" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="E299" s="20" t="s">
         <v>92</v>
@@ -15342,7 +15321,7 @@
         <v>386</v>
       </c>
       <c r="C300" s="20" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="D300" s="20"/>
       <c r="E300" s="20"/>
@@ -15359,14 +15338,14 @@
       <c r="P300" s="20"/>
       <c r="Q300" s="20"/>
       <c r="R300" s="20" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="S300" s="21"/>
       <c r="T300" s="19" t="s">
         <v>409</v>
       </c>
       <c r="U300" s="21" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="V300" s="20"/>
       <c r="W300" s="20"/>
@@ -15385,7 +15364,7 @@
         <v>386</v>
       </c>
       <c r="C301" s="20" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="D301" s="20"/>
       <c r="E301" s="20"/>
@@ -15402,14 +15381,14 @@
       <c r="P301" s="20"/>
       <c r="Q301" s="20"/>
       <c r="R301" s="20" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="S301" s="21"/>
       <c r="T301" s="19" t="s">
         <v>409</v>
       </c>
       <c r="U301" s="21" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="V301" s="20"/>
       <c r="W301" s="20"/>
@@ -15428,7 +15407,7 @@
         <v>386</v>
       </c>
       <c r="C302" s="20" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="D302" s="20"/>
       <c r="E302" s="20"/>
@@ -15445,14 +15424,14 @@
       <c r="P302" s="20"/>
       <c r="Q302" s="20"/>
       <c r="R302" s="20" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="S302" s="21"/>
       <c r="T302" s="19" t="s">
         <v>409</v>
       </c>
       <c r="U302" s="21" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="V302" s="20"/>
       <c r="W302" s="20"/>
@@ -15463,87 +15442,97 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="303" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:25" s="19" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A303" s="7">
-        <v>302</v>
-      </c>
-      <c r="B303" s="20" t="s">
-        <v>386</v>
-      </c>
-      <c r="C303" s="20" t="s">
-        <v>443</v>
-      </c>
-      <c r="D303" s="20"/>
-      <c r="E303" s="20"/>
-      <c r="F303" s="20"/>
-      <c r="G303" s="20"/>
-      <c r="H303" s="20"/>
-      <c r="I303" s="20"/>
-      <c r="J303" s="20"/>
-      <c r="K303" s="20"/>
-      <c r="L303" s="20"/>
-      <c r="M303" s="20"/>
-      <c r="N303" s="20"/>
-      <c r="O303" s="20"/>
-      <c r="P303" s="20"/>
-      <c r="Q303" s="20"/>
-      <c r="R303" s="20" t="s">
-        <v>468</v>
+        <v>304</v>
+      </c>
+      <c r="B303" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="C303" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="D303" s="21"/>
+      <c r="E303" s="21"/>
+      <c r="F303" s="21"/>
+      <c r="G303" s="21"/>
+      <c r="H303" s="21"/>
+      <c r="I303" s="21"/>
+      <c r="J303" s="21"/>
+      <c r="K303" s="21"/>
+      <c r="L303" s="21"/>
+      <c r="M303" s="21"/>
+      <c r="N303" s="21"/>
+      <c r="O303" s="21"/>
+      <c r="P303" s="21"/>
+      <c r="Q303" s="21"/>
+      <c r="R303" s="21" t="s">
+        <v>231</v>
       </c>
       <c r="S303" s="21"/>
-      <c r="T303" s="19"/>
-      <c r="U303" s="21"/>
-      <c r="V303" s="20" t="s">
-        <v>444</v>
-      </c>
-      <c r="W303" s="20"/>
-      <c r="X303" s="20"/>
-      <c r="Y303" s="20" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="304" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="T303" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="U303" s="29" t="s">
+        <v>477</v>
+      </c>
+      <c r="V303" s="21"/>
+      <c r="W303" s="21"/>
+      <c r="X303" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y303" s="21">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="304" spans="1:25" s="18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A304" s="7">
-        <v>303</v>
-      </c>
-      <c r="B304" s="20" t="s">
-        <v>386</v>
-      </c>
-      <c r="C304" s="20" t="s">
-        <v>443</v>
-      </c>
-      <c r="D304" s="20"/>
-      <c r="E304" s="20"/>
-      <c r="F304" s="20"/>
-      <c r="G304" s="20"/>
-      <c r="H304" s="20"/>
-      <c r="I304" s="20"/>
-      <c r="J304" s="20"/>
-      <c r="K304" s="20"/>
-      <c r="L304" s="20"/>
-      <c r="M304" s="20"/>
-      <c r="N304" s="20"/>
-      <c r="O304" s="20"/>
-      <c r="P304" s="20"/>
-      <c r="Q304" s="20"/>
-      <c r="R304" s="20" t="s">
-        <v>469</v>
+        <v>305</v>
+      </c>
+      <c r="B304" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="C304" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="D304" s="25"/>
+      <c r="E304" s="25"/>
+      <c r="F304" s="25"/>
+      <c r="G304" s="25"/>
+      <c r="H304" s="25"/>
+      <c r="I304" s="25"/>
+      <c r="J304" s="25"/>
+      <c r="K304" s="25"/>
+      <c r="L304" s="25"/>
+      <c r="M304" s="25"/>
+      <c r="N304" s="25"/>
+      <c r="O304" s="25"/>
+      <c r="P304" s="21"/>
+      <c r="Q304" s="25"/>
+      <c r="R304" s="21" t="s">
+        <v>231</v>
       </c>
       <c r="S304" s="21"/>
-      <c r="T304" s="19"/>
-      <c r="U304" s="21"/>
-      <c r="V304" s="20" t="s">
-        <v>444</v>
-      </c>
-      <c r="W304" s="20"/>
-      <c r="X304" s="20"/>
-      <c r="Y304" s="20" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="305" spans="1:25" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="T304" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="U304" s="25">
+        <v>1</v>
+      </c>
+      <c r="V304" s="25" t="s">
+        <v>344</v>
+      </c>
+      <c r="W304" s="25">
+        <v>2</v>
+      </c>
+      <c r="X304" s="25"/>
+      <c r="Y304" s="25">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="305" spans="1:25" s="18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A305" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B305" s="21" t="s">
         <v>388</v>
@@ -15551,20 +15540,20 @@
       <c r="C305" s="21" t="s">
         <v>388</v>
       </c>
-      <c r="D305" s="21"/>
-      <c r="E305" s="21"/>
-      <c r="F305" s="21"/>
-      <c r="G305" s="21"/>
-      <c r="H305" s="21"/>
-      <c r="I305" s="21"/>
-      <c r="J305" s="21"/>
-      <c r="K305" s="21"/>
-      <c r="L305" s="21"/>
-      <c r="M305" s="21"/>
-      <c r="N305" s="21"/>
-      <c r="O305" s="21"/>
+      <c r="D305" s="25"/>
+      <c r="E305" s="25"/>
+      <c r="F305" s="25"/>
+      <c r="G305" s="25"/>
+      <c r="H305" s="25"/>
+      <c r="I305" s="25"/>
+      <c r="J305" s="25"/>
+      <c r="K305" s="25"/>
+      <c r="L305" s="25"/>
+      <c r="M305" s="25"/>
+      <c r="N305" s="25"/>
+      <c r="O305" s="25"/>
       <c r="P305" s="21"/>
-      <c r="Q305" s="21"/>
+      <c r="Q305" s="25"/>
       <c r="R305" s="21" t="s">
         <v>231</v>
       </c>
@@ -15572,205 +15561,177 @@
       <c r="T305" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="U305" s="25">
-        <v>0</v>
-      </c>
-      <c r="V305" s="21"/>
-      <c r="W305" s="21"/>
-      <c r="X305" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y305" s="21">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="306" spans="1:25" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="U305" s="21">
+        <v>2</v>
+      </c>
+      <c r="V305" s="25"/>
+      <c r="W305" s="25"/>
+      <c r="X305" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y305" s="25">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="306" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A306" s="7">
-        <v>305</v>
-      </c>
-      <c r="B306" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="B306" s="20" t="s">
         <v>388</v>
       </c>
-      <c r="C306" s="21" t="s">
+      <c r="C306" s="20" t="s">
         <v>388</v>
       </c>
-      <c r="D306" s="25"/>
-      <c r="E306" s="25"/>
-      <c r="F306" s="25"/>
-      <c r="G306" s="25"/>
-      <c r="H306" s="25"/>
-      <c r="I306" s="25"/>
-      <c r="J306" s="25"/>
-      <c r="K306" s="25"/>
-      <c r="L306" s="25"/>
-      <c r="M306" s="25"/>
-      <c r="N306" s="25"/>
-      <c r="O306" s="25"/>
-      <c r="P306" s="21"/>
-      <c r="Q306" s="25"/>
-      <c r="R306" s="21" t="s">
-        <v>231</v>
-      </c>
-      <c r="S306" s="21"/>
-      <c r="T306" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="U306" s="25">
-        <v>1</v>
-      </c>
-      <c r="V306" s="25" t="s">
-        <v>344</v>
-      </c>
-      <c r="W306" s="25">
-        <v>2</v>
-      </c>
-      <c r="X306" s="25"/>
-      <c r="Y306" s="25">
-        <v>1602</v>
-      </c>
-    </row>
-    <row r="307" spans="1:25" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="D306" s="20" t="s">
+        <v>358</v>
+      </c>
+      <c r="E306" s="20"/>
+      <c r="F306" s="20"/>
+      <c r="G306" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H306" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I306" s="20"/>
+      <c r="J306" s="20"/>
+      <c r="K306" s="20"/>
+      <c r="L306" s="20"/>
+      <c r="M306" s="20"/>
+      <c r="N306" s="20"/>
+      <c r="O306" s="20"/>
+      <c r="P306" s="20"/>
+      <c r="Q306" s="20"/>
+      <c r="R306" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="S306" s="21" t="s">
+        <v>426</v>
+      </c>
+      <c r="T306" s="19"/>
+      <c r="U306" s="21"/>
+      <c r="V306" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="W306" s="20" t="s">
+        <v>340</v>
+      </c>
+      <c r="X306" s="20"/>
+      <c r="Y306" s="20">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="307" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A307" s="7">
-        <v>306</v>
-      </c>
-      <c r="B307" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="B307" s="20" t="s">
         <v>388</v>
       </c>
-      <c r="C307" s="21" t="s">
+      <c r="C307" s="20" t="s">
         <v>388</v>
       </c>
-      <c r="D307" s="25"/>
-      <c r="E307" s="25"/>
-      <c r="F307" s="25"/>
-      <c r="G307" s="25"/>
-      <c r="H307" s="25"/>
-      <c r="I307" s="25"/>
-      <c r="J307" s="25"/>
-      <c r="K307" s="25"/>
-      <c r="L307" s="25"/>
-      <c r="M307" s="25"/>
-      <c r="N307" s="25"/>
-      <c r="O307" s="25"/>
-      <c r="P307" s="21"/>
-      <c r="Q307" s="25"/>
-      <c r="R307" s="21" t="s">
-        <v>231</v>
+      <c r="D307" s="20" t="s">
+        <v>357</v>
+      </c>
+      <c r="E307" s="20"/>
+      <c r="F307" s="20"/>
+      <c r="G307" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H307" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I307" s="20"/>
+      <c r="J307" s="20"/>
+      <c r="K307" s="20"/>
+      <c r="L307" s="20"/>
+      <c r="M307" s="20"/>
+      <c r="N307" s="20"/>
+      <c r="O307" s="20"/>
+      <c r="P307" s="20"/>
+      <c r="Q307" s="20"/>
+      <c r="R307" s="20" t="s">
+        <v>229</v>
       </c>
       <c r="S307" s="21"/>
-      <c r="T307" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="U307" s="21">
-        <v>2</v>
-      </c>
-      <c r="V307" s="25"/>
-      <c r="W307" s="25"/>
-      <c r="X307" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y307" s="25">
-        <v>1603</v>
-      </c>
-    </row>
-    <row r="308" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="T307" s="19"/>
+      <c r="U307" s="21"/>
+      <c r="V307" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="W307" s="20" t="s">
+        <v>340</v>
+      </c>
+      <c r="X307" s="20"/>
+      <c r="Y307" s="20">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="308" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A308" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B308" s="20" t="s">
         <v>388</v>
       </c>
       <c r="C308" s="20" t="s">
-        <v>388</v>
-      </c>
-      <c r="D308" s="20" t="s">
-        <v>358</v>
-      </c>
-      <c r="E308" s="20"/>
-      <c r="F308" s="20"/>
-      <c r="G308" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="H308" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="I308" s="20"/>
-      <c r="J308" s="20"/>
-      <c r="K308" s="20"/>
-      <c r="L308" s="20"/>
-      <c r="M308" s="20"/>
-      <c r="N308" s="20"/>
-      <c r="O308" s="20"/>
+        <v>386</v>
+      </c>
+      <c r="D308" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E308" s="20" t="s">
+        <v>94</v>
+      </c>
       <c r="P308" s="20"/>
-      <c r="Q308" s="20"/>
       <c r="R308" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="S308" s="21" t="s">
-        <v>426</v>
-      </c>
-      <c r="T308" s="19"/>
-      <c r="U308" s="21"/>
-      <c r="V308" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="W308" s="20" t="s">
-        <v>340</v>
-      </c>
-      <c r="X308" s="20"/>
-      <c r="Y308" s="20">
-        <v>1604</v>
-      </c>
-    </row>
-    <row r="309" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="S308" s="25"/>
+      <c r="T308" s="18"/>
+      <c r="U308" s="25"/>
+      <c r="X308" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y308" s="1" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="309" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A309" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B309" s="20" t="s">
         <v>388</v>
       </c>
       <c r="C309" s="20" t="s">
-        <v>388</v>
-      </c>
-      <c r="D309" s="20" t="s">
-        <v>357</v>
-      </c>
-      <c r="E309" s="20"/>
-      <c r="F309" s="20"/>
-      <c r="G309" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="H309" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="I309" s="20"/>
-      <c r="J309" s="20"/>
-      <c r="K309" s="20"/>
-      <c r="L309" s="20"/>
-      <c r="M309" s="20"/>
-      <c r="N309" s="20"/>
-      <c r="O309" s="20"/>
+        <v>393</v>
+      </c>
+      <c r="D309" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E309" s="20" t="s">
+        <v>94</v>
+      </c>
       <c r="P309" s="20"/>
-      <c r="Q309" s="20"/>
       <c r="R309" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="S309" s="21"/>
-      <c r="T309" s="19"/>
-      <c r="U309" s="21"/>
-      <c r="V309" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="W309" s="20" t="s">
-        <v>340</v>
-      </c>
-      <c r="X309" s="20"/>
-      <c r="Y309" s="20">
-        <v>1604</v>
+      <c r="S309" s="25"/>
+      <c r="T309" s="18"/>
+      <c r="U309" s="25"/>
+      <c r="X309" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y309" s="1" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="310" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A310" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B310" s="20" t="s">
         <v>388</v>
@@ -15779,7 +15740,7 @@
         <v>386</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E310" s="20" t="s">
         <v>94</v>
@@ -15792,15 +15753,15 @@
       <c r="T310" s="18"/>
       <c r="U310" s="25"/>
       <c r="X310" s="1" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="Y310" s="1" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="311" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A311" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B311" s="20" t="s">
         <v>388</v>
@@ -15809,7 +15770,7 @@
         <v>393</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E311" s="20" t="s">
         <v>94</v>
@@ -15822,15 +15783,15 @@
       <c r="T311" s="18"/>
       <c r="U311" s="25"/>
       <c r="X311" s="1" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="Y311" s="1" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="312" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A312" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B312" s="20" t="s">
         <v>388</v>
@@ -15839,7 +15800,7 @@
         <v>386</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E312" s="20" t="s">
         <v>94</v>
@@ -15852,15 +15813,15 @@
       <c r="T312" s="18"/>
       <c r="U312" s="25"/>
       <c r="X312" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="Y312" s="1" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="313" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A313" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B313" s="20" t="s">
         <v>388</v>
@@ -15869,7 +15830,7 @@
         <v>393</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E313" s="20" t="s">
         <v>94</v>
@@ -15882,27 +15843,33 @@
       <c r="T313" s="18"/>
       <c r="U313" s="25"/>
       <c r="X313" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="Y313" s="1" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="314" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A314" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B314" s="20" t="s">
         <v>388</v>
       </c>
       <c r="C314" s="20" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>69</v>
+        <v>361</v>
       </c>
       <c r="E314" s="20" t="s">
-        <v>94</v>
+        <v>254</v>
+      </c>
+      <c r="G314" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H314" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="P314" s="20"/>
       <c r="R314" s="20" t="s">
@@ -15911,28 +15878,35 @@
       <c r="S314" s="25"/>
       <c r="T314" s="18"/>
       <c r="U314" s="25"/>
-      <c r="X314" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y314" s="1" t="s">
-        <v>476</v>
+      <c r="V314" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="W314" s="20" t="s">
+        <v>339</v>
+      </c>
+      <c r="Y314" s="1">
+        <v>1605</v>
       </c>
     </row>
     <row r="315" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A315" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B315" s="20" t="s">
         <v>388</v>
       </c>
       <c r="C315" s="20" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E315" s="20" t="s">
-        <v>94</v>
+        <v>362</v>
+      </c>
+      <c r="E315" s="20"/>
+      <c r="G315" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H315" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="P315" s="20"/>
       <c r="R315" s="20" t="s">
@@ -15941,101 +15915,122 @@
       <c r="S315" s="25"/>
       <c r="T315" s="18"/>
       <c r="U315" s="25"/>
-      <c r="X315" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y315" s="1" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="316" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="V315" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="W315" s="20" t="s">
+        <v>340</v>
+      </c>
+      <c r="Y315" s="1">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="316" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A316" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B316" s="20" t="s">
         <v>388</v>
       </c>
       <c r="C316" s="20" t="s">
-        <v>393</v>
-      </c>
-      <c r="D316" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="E316" s="20" t="s">
-        <v>254</v>
-      </c>
-      <c r="G316" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H316" s="1" t="s">
-        <v>48</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="D316" s="20" t="s">
+        <v>359</v>
+      </c>
+      <c r="E316" s="20"/>
+      <c r="F316" s="20"/>
+      <c r="G316" s="20"/>
+      <c r="H316" s="20"/>
+      <c r="I316" s="20"/>
+      <c r="J316" s="20"/>
+      <c r="K316" s="20"/>
+      <c r="L316" s="20"/>
+      <c r="M316" s="20"/>
+      <c r="N316" s="20"/>
+      <c r="O316" s="20"/>
       <c r="P316" s="20"/>
+      <c r="Q316" s="20"/>
       <c r="R316" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="S316" s="25"/>
-      <c r="T316" s="18"/>
-      <c r="U316" s="25"/>
+        <v>365</v>
+      </c>
+      <c r="S316" s="21"/>
+      <c r="T316" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="U316" s="21" t="s">
+        <v>399</v>
+      </c>
       <c r="V316" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="W316" s="20" t="s">
-        <v>339</v>
-      </c>
-      <c r="Y316" s="1">
-        <v>1605</v>
-      </c>
-    </row>
-    <row r="317" spans="1:25" x14ac:dyDescent="0.2">
+        <v>345</v>
+      </c>
+      <c r="W316" s="20">
+        <v>3</v>
+      </c>
+      <c r="X316" s="20"/>
+      <c r="Y316" s="20">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="317" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A317" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B317" s="20" t="s">
         <v>388</v>
       </c>
       <c r="C317" s="20" t="s">
-        <v>388</v>
-      </c>
-      <c r="D317" s="1" t="s">
-        <v>362</v>
+        <v>393</v>
+      </c>
+      <c r="D317" s="20" t="s">
+        <v>263</v>
       </c>
       <c r="E317" s="20"/>
-      <c r="G317" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H317" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="F317" s="20"/>
+      <c r="G317" s="20"/>
+      <c r="H317" s="20"/>
+      <c r="I317" s="20"/>
+      <c r="J317" s="20"/>
+      <c r="K317" s="20"/>
+      <c r="L317" s="20"/>
+      <c r="M317" s="20"/>
+      <c r="N317" s="20"/>
+      <c r="O317" s="20"/>
       <c r="P317" s="20"/>
+      <c r="Q317" s="20"/>
       <c r="R317" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="S317" s="25"/>
-      <c r="T317" s="18"/>
-      <c r="U317" s="25"/>
+        <v>365</v>
+      </c>
+      <c r="S317" s="21"/>
+      <c r="T317" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="U317" s="21" t="s">
+        <v>399</v>
+      </c>
       <c r="V317" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="W317" s="20" t="s">
-        <v>340</v>
-      </c>
-      <c r="Y317" s="1">
-        <v>1606</v>
+        <v>345</v>
+      </c>
+      <c r="W317" s="20">
+        <v>4</v>
+      </c>
+      <c r="X317" s="20"/>
+      <c r="Y317" s="20">
+        <v>1608</v>
       </c>
     </row>
     <row r="318" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A318" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B318" s="20" t="s">
         <v>388</v>
       </c>
       <c r="C318" s="20" t="s">
-        <v>388</v>
+        <v>467</v>
       </c>
       <c r="D318" s="20" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="E318" s="20"/>
       <c r="F318" s="20"/>
@@ -16051,7 +16046,7 @@
       <c r="P318" s="20"/>
       <c r="Q318" s="20"/>
       <c r="R318" s="20" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="S318" s="21"/>
       <c r="T318" s="19" t="s">
@@ -16060,29 +16055,27 @@
       <c r="U318" s="21" t="s">
         <v>399</v>
       </c>
-      <c r="V318" s="20" t="s">
-        <v>345</v>
-      </c>
-      <c r="W318" s="20">
-        <v>3</v>
-      </c>
-      <c r="X318" s="20"/>
+      <c r="V318" s="20"/>
+      <c r="W318" s="20"/>
+      <c r="X318" s="20" t="s">
+        <v>47</v>
+      </c>
       <c r="Y318" s="20">
-        <v>1607</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="319" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A319" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B319" s="20" t="s">
         <v>388</v>
       </c>
       <c r="C319" s="20" t="s">
-        <v>393</v>
+        <v>467</v>
       </c>
       <c r="D319" s="20" t="s">
-        <v>263</v>
+        <v>367</v>
       </c>
       <c r="E319" s="20"/>
       <c r="F319" s="20"/>
@@ -16098,43 +16091,45 @@
       <c r="P319" s="20"/>
       <c r="Q319" s="20"/>
       <c r="R319" s="20" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="S319" s="21"/>
       <c r="T319" s="19" t="s">
         <v>409</v>
       </c>
       <c r="U319" s="21" t="s">
-        <v>399</v>
-      </c>
-      <c r="V319" s="20" t="s">
-        <v>345</v>
-      </c>
-      <c r="W319" s="20">
-        <v>4</v>
-      </c>
-      <c r="X319" s="20"/>
+        <v>400</v>
+      </c>
+      <c r="V319" s="20"/>
+      <c r="W319" s="20"/>
+      <c r="X319" s="20" t="s">
+        <v>264</v>
+      </c>
       <c r="Y319" s="20">
-        <v>1608</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="320" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A320" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B320" s="20" t="s">
         <v>388</v>
       </c>
       <c r="C320" s="20" t="s">
-        <v>443</v>
+        <v>388</v>
       </c>
       <c r="D320" s="20" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="E320" s="20"/>
       <c r="F320" s="20"/>
-      <c r="G320" s="20"/>
-      <c r="H320" s="20"/>
+      <c r="G320" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H320" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="I320" s="20"/>
       <c r="J320" s="20"/>
       <c r="K320" s="20"/>
@@ -16145,41 +16140,45 @@
       <c r="P320" s="20"/>
       <c r="Q320" s="20"/>
       <c r="R320" s="20" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="S320" s="21"/>
       <c r="T320" s="19" t="s">
-        <v>409</v>
-      </c>
-      <c r="U320" s="21" t="s">
-        <v>399</v>
-      </c>
-      <c r="V320" s="20"/>
-      <c r="W320" s="20"/>
-      <c r="X320" s="20" t="s">
-        <v>47</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="U320" s="21"/>
+      <c r="V320" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="W320" s="20" t="s">
+        <v>340</v>
+      </c>
+      <c r="X320" s="20"/>
       <c r="Y320" s="20">
-        <v>1609</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="321" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A321" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B321" s="20" t="s">
         <v>388</v>
       </c>
       <c r="C321" s="20" t="s">
-        <v>443</v>
+        <v>388</v>
       </c>
       <c r="D321" s="20" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="E321" s="20"/>
       <c r="F321" s="20"/>
-      <c r="G321" s="20"/>
-      <c r="H321" s="20"/>
+      <c r="G321" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H321" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="I321" s="20"/>
       <c r="J321" s="20"/>
       <c r="K321" s="20"/>
@@ -16190,27 +16189,25 @@
       <c r="P321" s="20"/>
       <c r="Q321" s="20"/>
       <c r="R321" s="20" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="S321" s="21"/>
-      <c r="T321" s="19" t="s">
-        <v>409</v>
-      </c>
-      <c r="U321" s="21" t="s">
-        <v>400</v>
-      </c>
-      <c r="V321" s="20"/>
-      <c r="W321" s="20"/>
-      <c r="X321" s="20" t="s">
-        <v>264</v>
-      </c>
+      <c r="T321" s="19"/>
+      <c r="U321" s="21"/>
+      <c r="V321" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="W321" s="20" t="s">
+        <v>340</v>
+      </c>
+      <c r="X321" s="20"/>
       <c r="Y321" s="20">
-        <v>1610</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="322" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A322" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B322" s="20" t="s">
         <v>388</v>
@@ -16219,16 +16216,12 @@
         <v>388</v>
       </c>
       <c r="D322" s="20" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E322" s="20"/>
       <c r="F322" s="20"/>
-      <c r="G322" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="H322" s="20" t="s">
-        <v>48</v>
-      </c>
+      <c r="G322" s="20"/>
+      <c r="H322" s="20"/>
       <c r="I322" s="20"/>
       <c r="J322" s="20"/>
       <c r="K322" s="20"/>
@@ -16239,27 +16232,27 @@
       <c r="P322" s="20"/>
       <c r="Q322" s="20"/>
       <c r="R322" s="20" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="S322" s="21"/>
-      <c r="T322" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="U322" s="21"/>
-      <c r="V322" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="W322" s="20" t="s">
-        <v>340</v>
-      </c>
-      <c r="X322" s="20"/>
+      <c r="T322" s="18" t="s">
+        <v>409</v>
+      </c>
+      <c r="U322" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="V322" s="20"/>
+      <c r="W322" s="20"/>
+      <c r="X322" s="20" t="s">
+        <v>56</v>
+      </c>
       <c r="Y322" s="20">
-        <v>1611</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="323" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A323" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B323" s="20" t="s">
         <v>388</v>
@@ -16268,16 +16261,12 @@
         <v>388</v>
       </c>
       <c r="D323" s="20" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E323" s="20"/>
       <c r="F323" s="20"/>
-      <c r="G323" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="H323" s="20" t="s">
-        <v>48</v>
-      </c>
+      <c r="G323" s="20"/>
+      <c r="H323" s="20"/>
       <c r="I323" s="20"/>
       <c r="J323" s="20"/>
       <c r="K323" s="20"/>
@@ -16288,25 +16277,27 @@
       <c r="P323" s="20"/>
       <c r="Q323" s="20"/>
       <c r="R323" s="20" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="S323" s="21"/>
-      <c r="T323" s="19"/>
-      <c r="U323" s="21"/>
-      <c r="V323" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="W323" s="20" t="s">
-        <v>340</v>
-      </c>
-      <c r="X323" s="20"/>
+      <c r="T323" s="18" t="s">
+        <v>409</v>
+      </c>
+      <c r="U323" s="21" t="s">
+        <v>400</v>
+      </c>
+      <c r="V323" s="20"/>
+      <c r="W323" s="20"/>
+      <c r="X323" s="20" t="s">
+        <v>210</v>
+      </c>
       <c r="Y323" s="20">
-        <v>1611</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="324" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A324" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B324" s="20" t="s">
         <v>388</v>
@@ -16315,7 +16306,7 @@
         <v>388</v>
       </c>
       <c r="D324" s="20" t="s">
-        <v>359</v>
+        <v>263</v>
       </c>
       <c r="E324" s="20"/>
       <c r="F324" s="20"/>
@@ -16343,15 +16334,15 @@
       <c r="V324" s="20"/>
       <c r="W324" s="20"/>
       <c r="X324" s="20" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="Y324" s="20">
-        <v>1612</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="325" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A325" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B325" s="20" t="s">
         <v>388</v>
@@ -16360,7 +16351,7 @@
         <v>388</v>
       </c>
       <c r="D325" s="20" t="s">
-        <v>359</v>
+        <v>263</v>
       </c>
       <c r="E325" s="20"/>
       <c r="F325" s="20"/>
@@ -16388,24 +16379,24 @@
       <c r="V325" s="20"/>
       <c r="W325" s="20"/>
       <c r="X325" s="20" t="s">
-        <v>210</v>
+        <v>45</v>
       </c>
       <c r="Y325" s="20">
-        <v>1613</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="326" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A326" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B326" s="20" t="s">
         <v>388</v>
       </c>
       <c r="C326" s="20" t="s">
-        <v>388</v>
+        <v>467</v>
       </c>
       <c r="D326" s="20" t="s">
-        <v>263</v>
+        <v>367</v>
       </c>
       <c r="E326" s="20"/>
       <c r="F326" s="20"/>
@@ -16433,24 +16424,24 @@
       <c r="V326" s="20"/>
       <c r="W326" s="20"/>
       <c r="X326" s="20" t="s">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="Y326" s="20">
-        <v>1614</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="327" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A327" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B327" s="20" t="s">
         <v>388</v>
       </c>
       <c r="C327" s="20" t="s">
-        <v>388</v>
+        <v>467</v>
       </c>
       <c r="D327" s="20" t="s">
-        <v>263</v>
+        <v>367</v>
       </c>
       <c r="E327" s="20"/>
       <c r="F327" s="20"/>
@@ -16478,24 +16469,24 @@
       <c r="V327" s="20"/>
       <c r="W327" s="20"/>
       <c r="X327" s="20" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Y327" s="20">
-        <v>1615</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="328" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A328" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B328" s="20" t="s">
         <v>388</v>
       </c>
       <c r="C328" s="20" t="s">
-        <v>443</v>
+        <v>467</v>
       </c>
       <c r="D328" s="20" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E328" s="20"/>
       <c r="F328" s="20"/>
@@ -16511,36 +16502,36 @@
       <c r="P328" s="20"/>
       <c r="Q328" s="20"/>
       <c r="R328" s="20" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="S328" s="21"/>
       <c r="T328" s="18" t="s">
-        <v>409</v>
-      </c>
-      <c r="U328" s="21" t="s">
-        <v>399</v>
+        <v>123</v>
+      </c>
+      <c r="U328" s="25" t="s">
+        <v>293</v>
       </c>
       <c r="V328" s="20"/>
       <c r="W328" s="20"/>
       <c r="X328" s="20" t="s">
-        <v>264</v>
+        <v>44</v>
       </c>
       <c r="Y328" s="20">
-        <v>1616</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="329" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A329" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B329" s="20" t="s">
         <v>388</v>
       </c>
       <c r="C329" s="20" t="s">
-        <v>443</v>
+        <v>467</v>
       </c>
       <c r="D329" s="20" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E329" s="20"/>
       <c r="F329" s="20"/>
@@ -16556,33 +16547,33 @@
       <c r="P329" s="20"/>
       <c r="Q329" s="20"/>
       <c r="R329" s="20" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="S329" s="21"/>
       <c r="T329" s="18" t="s">
-        <v>409</v>
+        <v>123</v>
       </c>
       <c r="U329" s="21" t="s">
-        <v>400</v>
+        <v>291</v>
       </c>
       <c r="V329" s="20"/>
       <c r="W329" s="20"/>
       <c r="X329" s="20" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Y329" s="20">
-        <v>1617</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="330" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A330" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B330" s="20" t="s">
         <v>388</v>
       </c>
       <c r="C330" s="20" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="D330" s="20" t="s">
         <v>368</v>
@@ -16601,36 +16592,36 @@
       <c r="P330" s="20"/>
       <c r="Q330" s="20"/>
       <c r="R330" s="20" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="S330" s="21"/>
       <c r="T330" s="18" t="s">
         <v>123</v>
       </c>
       <c r="U330" s="25" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="V330" s="20"/>
       <c r="W330" s="20"/>
       <c r="X330" s="20" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Y330" s="20">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="331" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A331" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B331" s="20" t="s">
         <v>388</v>
       </c>
       <c r="C331" s="20" t="s">
-        <v>475</v>
+        <v>393</v>
       </c>
       <c r="D331" s="20" t="s">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="E331" s="20"/>
       <c r="F331" s="20"/>
@@ -16646,36 +16637,36 @@
       <c r="P331" s="20"/>
       <c r="Q331" s="20"/>
       <c r="R331" s="20" t="s">
-        <v>365</v>
+        <v>403</v>
       </c>
       <c r="S331" s="21"/>
-      <c r="T331" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="U331" s="21" t="s">
-        <v>291</v>
+      <c r="T331" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="U331" s="25" t="s">
+        <v>397</v>
       </c>
       <c r="V331" s="20"/>
       <c r="W331" s="20"/>
       <c r="X331" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y331" s="20">
-        <v>1618</v>
+        <v>47</v>
+      </c>
+      <c r="Y331" s="20" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="332" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A332" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B332" s="20" t="s">
         <v>388</v>
       </c>
       <c r="C332" s="20" t="s">
-        <v>475</v>
+        <v>393</v>
       </c>
       <c r="D332" s="20" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="E332" s="20"/>
       <c r="F332" s="20"/>
@@ -16691,27 +16682,27 @@
       <c r="P332" s="20"/>
       <c r="Q332" s="20"/>
       <c r="R332" s="20" t="s">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="S332" s="21"/>
-      <c r="T332" s="18" t="s">
-        <v>123</v>
+      <c r="T332" s="19" t="s">
+        <v>409</v>
       </c>
       <c r="U332" s="25" t="s">
-        <v>292</v>
+        <v>397</v>
       </c>
       <c r="V332" s="20"/>
       <c r="W332" s="20"/>
       <c r="X332" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y332" s="20">
-        <v>1619</v>
+        <v>335</v>
+      </c>
+      <c r="Y332" s="20" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="333" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A333" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B333" s="20" t="s">
         <v>388</v>
@@ -16736,27 +16727,27 @@
       <c r="P333" s="20"/>
       <c r="Q333" s="20"/>
       <c r="R333" s="20" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="S333" s="21"/>
       <c r="T333" s="19" t="s">
         <v>409</v>
       </c>
       <c r="U333" s="25" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="V333" s="20"/>
       <c r="W333" s="20"/>
       <c r="X333" s="20" t="s">
-        <v>47</v>
+        <v>264</v>
       </c>
       <c r="Y333" s="20" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="334" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A334" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B334" s="20" t="s">
         <v>388</v>
@@ -16781,27 +16772,27 @@
       <c r="P334" s="20"/>
       <c r="Q334" s="20"/>
       <c r="R334" s="20" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="S334" s="21"/>
       <c r="T334" s="19" t="s">
         <v>409</v>
       </c>
       <c r="U334" s="25" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="V334" s="20"/>
       <c r="W334" s="20"/>
       <c r="X334" s="20" t="s">
-        <v>335</v>
+        <v>46</v>
       </c>
       <c r="Y334" s="20" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="335" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A335" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B335" s="20" t="s">
         <v>388</v>
@@ -16810,7 +16801,7 @@
         <v>393</v>
       </c>
       <c r="D335" s="20" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="E335" s="20"/>
       <c r="F335" s="20"/>
@@ -16826,27 +16817,23 @@
       <c r="P335" s="20"/>
       <c r="Q335" s="20"/>
       <c r="R335" s="20" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="S335" s="21"/>
-      <c r="T335" s="19" t="s">
-        <v>409</v>
-      </c>
-      <c r="U335" s="25" t="s">
-        <v>398</v>
-      </c>
+      <c r="T335" s="18"/>
+      <c r="U335" s="25"/>
       <c r="V335" s="20"/>
       <c r="W335" s="20"/>
       <c r="X335" s="20" t="s">
-        <v>264</v>
+        <v>142</v>
       </c>
       <c r="Y335" s="20" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="336" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A336" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B336" s="20" t="s">
         <v>388</v>
@@ -16855,7 +16842,7 @@
         <v>393</v>
       </c>
       <c r="D336" s="20" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="E336" s="20"/>
       <c r="F336" s="20"/>
@@ -16871,27 +16858,25 @@
       <c r="P336" s="20"/>
       <c r="Q336" s="20"/>
       <c r="R336" s="20" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="S336" s="21"/>
-      <c r="T336" s="19" t="s">
-        <v>409</v>
-      </c>
-      <c r="U336" s="25" t="s">
-        <v>398</v>
-      </c>
-      <c r="V336" s="20"/>
-      <c r="W336" s="20"/>
-      <c r="X336" s="20" t="s">
-        <v>46</v>
-      </c>
+      <c r="T336" s="18"/>
+      <c r="U336" s="25"/>
+      <c r="V336" s="20" t="s">
+        <v>345</v>
+      </c>
+      <c r="W336" s="20">
+        <v>4</v>
+      </c>
+      <c r="X336" s="20"/>
       <c r="Y336" s="20" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="337" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A337" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B337" s="20" t="s">
         <v>388</v>
@@ -16900,7 +16885,7 @@
         <v>393</v>
       </c>
       <c r="D337" s="20" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="E337" s="20"/>
       <c r="F337" s="20"/>
@@ -16916,7 +16901,7 @@
       <c r="P337" s="20"/>
       <c r="Q337" s="20"/>
       <c r="R337" s="20" t="s">
-        <v>405</v>
+        <v>441</v>
       </c>
       <c r="S337" s="21"/>
       <c r="T337" s="18"/>
@@ -16924,15 +16909,15 @@
       <c r="V337" s="20"/>
       <c r="W337" s="20"/>
       <c r="X337" s="20" t="s">
-        <v>142</v>
+        <v>264</v>
       </c>
       <c r="Y337" s="20" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="338" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A338" s="7">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B338" s="20" t="s">
         <v>388</v>
@@ -16941,7 +16926,7 @@
         <v>393</v>
       </c>
       <c r="D338" s="20" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="E338" s="20"/>
       <c r="F338" s="20"/>
@@ -16957,25 +16942,23 @@
       <c r="P338" s="20"/>
       <c r="Q338" s="20"/>
       <c r="R338" s="20" t="s">
-        <v>405</v>
+        <v>441</v>
       </c>
       <c r="S338" s="21"/>
       <c r="T338" s="18"/>
       <c r="U338" s="25"/>
-      <c r="V338" s="20" t="s">
-        <v>345</v>
-      </c>
-      <c r="W338" s="20">
-        <v>4</v>
-      </c>
-      <c r="X338" s="20"/>
+      <c r="V338" s="20"/>
+      <c r="W338" s="20"/>
+      <c r="X338" s="20" t="s">
+        <v>46</v>
+      </c>
       <c r="Y338" s="20" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="339" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A339" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B339" s="20" t="s">
         <v>388</v>
@@ -17000,7 +16983,7 @@
       <c r="P339" s="20"/>
       <c r="Q339" s="20"/>
       <c r="R339" s="20" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="S339" s="21"/>
       <c r="T339" s="18"/>
@@ -17008,15 +16991,15 @@
       <c r="V339" s="20"/>
       <c r="W339" s="20"/>
       <c r="X339" s="20" t="s">
-        <v>264</v>
+        <v>47</v>
       </c>
       <c r="Y339" s="20" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="340" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A340" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B340" s="20" t="s">
         <v>388</v>
@@ -17041,7 +17024,7 @@
       <c r="P340" s="20"/>
       <c r="Q340" s="20"/>
       <c r="R340" s="20" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="S340" s="21"/>
       <c r="T340" s="18"/>
@@ -17049,15 +17032,15 @@
       <c r="V340" s="20"/>
       <c r="W340" s="20"/>
       <c r="X340" s="20" t="s">
-        <v>46</v>
+        <v>335</v>
       </c>
       <c r="Y340" s="20" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="341" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A341" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B341" s="20" t="s">
         <v>388</v>
@@ -17065,9 +17048,7 @@
       <c r="C341" s="20" t="s">
         <v>393</v>
       </c>
-      <c r="D341" s="20" t="s">
-        <v>394</v>
-      </c>
+      <c r="D341" s="20"/>
       <c r="E341" s="20"/>
       <c r="F341" s="20"/>
       <c r="G341" s="20"/>
@@ -17082,7 +17063,7 @@
       <c r="P341" s="20"/>
       <c r="Q341" s="20"/>
       <c r="R341" s="20" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="S341" s="21"/>
       <c r="T341" s="18"/>
@@ -17090,15 +17071,15 @@
       <c r="V341" s="20"/>
       <c r="W341" s="20"/>
       <c r="X341" s="20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Y341" s="20" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="342" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A342" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B342" s="20" t="s">
         <v>388</v>
@@ -17106,9 +17087,7 @@
       <c r="C342" s="20" t="s">
         <v>393</v>
       </c>
-      <c r="D342" s="20" t="s">
-        <v>375</v>
-      </c>
+      <c r="D342" s="20"/>
       <c r="E342" s="20"/>
       <c r="F342" s="20"/>
       <c r="G342" s="20"/>
@@ -17123,7 +17102,7 @@
       <c r="P342" s="20"/>
       <c r="Q342" s="20"/>
       <c r="R342" s="20" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="S342" s="21"/>
       <c r="T342" s="18"/>
@@ -17134,18 +17113,18 @@
         <v>335</v>
       </c>
       <c r="Y342" s="20" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="343" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A343" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B343" s="20" t="s">
         <v>388</v>
       </c>
       <c r="C343" s="20" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="D343" s="20"/>
       <c r="E343" s="20"/>
@@ -17162,29 +17141,33 @@
       <c r="P343" s="20"/>
       <c r="Q343" s="20"/>
       <c r="R343" s="20" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="S343" s="21"/>
-      <c r="T343" s="18"/>
-      <c r="U343" s="25"/>
+      <c r="T343" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="U343" s="21" t="s">
+        <v>291</v>
+      </c>
       <c r="V343" s="20"/>
       <c r="W343" s="20"/>
       <c r="X343" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y343" s="20" t="s">
-        <v>476</v>
+        <v>33</v>
+      </c>
+      <c r="Y343" s="20">
+        <v>1620</v>
       </c>
     </row>
     <row r="344" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A344" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B344" s="20" t="s">
         <v>388</v>
       </c>
       <c r="C344" s="20" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="D344" s="20"/>
       <c r="E344" s="20"/>
@@ -17201,23 +17184,27 @@
       <c r="P344" s="20"/>
       <c r="Q344" s="20"/>
       <c r="R344" s="20" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="S344" s="21"/>
-      <c r="T344" s="18"/>
-      <c r="U344" s="25"/>
+      <c r="T344" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="U344" s="21" t="s">
+        <v>293</v>
+      </c>
       <c r="V344" s="20"/>
       <c r="W344" s="20"/>
       <c r="X344" s="20" t="s">
-        <v>335</v>
-      </c>
-      <c r="Y344" s="20" t="s">
-        <v>476</v>
+        <v>33</v>
+      </c>
+      <c r="Y344" s="20">
+        <v>1621</v>
       </c>
     </row>
     <row r="345" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A345" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B345" s="20" t="s">
         <v>388</v>
@@ -17240,35 +17227,35 @@
       <c r="P345" s="20"/>
       <c r="Q345" s="20"/>
       <c r="R345" s="20" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="S345" s="21"/>
-      <c r="T345" s="19" t="s">
-        <v>454</v>
-      </c>
-      <c r="U345" s="21" t="s">
-        <v>291</v>
-      </c>
-      <c r="V345" s="20"/>
-      <c r="W345" s="20"/>
-      <c r="X345" s="20" t="s">
-        <v>33</v>
-      </c>
+      <c r="T345" s="19"/>
+      <c r="U345" s="21"/>
+      <c r="V345" s="20" t="s">
+        <v>345</v>
+      </c>
+      <c r="W345" s="20">
+        <v>5</v>
+      </c>
+      <c r="X345" s="20"/>
       <c r="Y345" s="20">
-        <v>1620</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="346" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A346" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B346" s="20" t="s">
         <v>388</v>
       </c>
       <c r="C346" s="20" t="s">
-        <v>388</v>
-      </c>
-      <c r="D346" s="20"/>
+        <v>393</v>
+      </c>
+      <c r="D346" s="20" t="s">
+        <v>204</v>
+      </c>
       <c r="E346" s="20"/>
       <c r="F346" s="20"/>
       <c r="G346" s="20"/>
@@ -17283,35 +17270,33 @@
       <c r="P346" s="20"/>
       <c r="Q346" s="20"/>
       <c r="R346" s="20" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="S346" s="21"/>
-      <c r="T346" s="19" t="s">
-        <v>454</v>
-      </c>
-      <c r="U346" s="21" t="s">
-        <v>293</v>
-      </c>
+      <c r="T346" s="19"/>
+      <c r="U346" s="21"/>
       <c r="V346" s="20"/>
       <c r="W346" s="20"/>
       <c r="X346" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y346" s="20">
-        <v>1621</v>
+        <v>68</v>
+      </c>
+      <c r="Y346" s="20" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="347" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A347" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B347" s="20" t="s">
         <v>388</v>
       </c>
       <c r="C347" s="20" t="s">
-        <v>388</v>
-      </c>
-      <c r="D347" s="20"/>
+        <v>393</v>
+      </c>
+      <c r="D347" s="20" t="s">
+        <v>450</v>
+      </c>
       <c r="E347" s="20"/>
       <c r="F347" s="20"/>
       <c r="G347" s="20"/>
@@ -17331,20 +17316,18 @@
       <c r="S347" s="21"/>
       <c r="T347" s="19"/>
       <c r="U347" s="21"/>
-      <c r="V347" s="20" t="s">
-        <v>345</v>
-      </c>
-      <c r="W347" s="20">
-        <v>5</v>
-      </c>
-      <c r="X347" s="20"/>
-      <c r="Y347" s="20">
-        <v>1622</v>
+      <c r="V347" s="20"/>
+      <c r="W347" s="20"/>
+      <c r="X347" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="Y347" s="20" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="348" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A348" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B348" s="20" t="s">
         <v>388</v>
@@ -17353,12 +17336,16 @@
         <v>393</v>
       </c>
       <c r="D348" s="20" t="s">
-        <v>204</v>
+        <v>451</v>
       </c>
       <c r="E348" s="20"/>
       <c r="F348" s="20"/>
-      <c r="G348" s="20"/>
-      <c r="H348" s="20"/>
+      <c r="G348" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H348" s="20" t="s">
+        <v>59</v>
+      </c>
       <c r="I348" s="20"/>
       <c r="J348" s="20"/>
       <c r="K348" s="20"/>
@@ -17369,23 +17356,27 @@
       <c r="P348" s="20"/>
       <c r="Q348" s="20"/>
       <c r="R348" s="20" t="s">
-        <v>460</v>
-      </c>
-      <c r="S348" s="21"/>
+        <v>454</v>
+      </c>
+      <c r="S348" s="21" t="s">
+        <v>426</v>
+      </c>
       <c r="T348" s="19"/>
       <c r="U348" s="21"/>
-      <c r="V348" s="20"/>
-      <c r="W348" s="20"/>
-      <c r="X348" s="20" t="s">
-        <v>68</v>
-      </c>
+      <c r="V348" s="20" t="s">
+        <v>345</v>
+      </c>
+      <c r="W348" s="20">
+        <v>6</v>
+      </c>
+      <c r="X348" s="20"/>
       <c r="Y348" s="20" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="349" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A349" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B349" s="20" t="s">
         <v>388</v>
@@ -17393,9 +17384,7 @@
       <c r="C349" s="20" t="s">
         <v>393</v>
       </c>
-      <c r="D349" s="20" t="s">
-        <v>457</v>
-      </c>
+      <c r="D349" s="20"/>
       <c r="E349" s="20"/>
       <c r="F349" s="20"/>
       <c r="G349" s="20"/>
@@ -17410,7 +17399,7 @@
       <c r="P349" s="20"/>
       <c r="Q349" s="20"/>
       <c r="R349" s="20" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="S349" s="21"/>
       <c r="T349" s="19"/>
@@ -17421,30 +17410,24 @@
         <v>142</v>
       </c>
       <c r="Y349" s="20" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="350" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A350" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B350" s="20" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C350" s="20" t="s">
-        <v>393</v>
-      </c>
-      <c r="D350" s="20" t="s">
-        <v>458</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="D350" s="20"/>
       <c r="E350" s="20"/>
       <c r="F350" s="20"/>
-      <c r="G350" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="H350" s="20" t="s">
-        <v>59</v>
-      </c>
+      <c r="G350" s="20"/>
+      <c r="H350" s="20"/>
       <c r="I350" s="20"/>
       <c r="J350" s="20"/>
       <c r="K350" s="20"/>
@@ -17455,66 +17438,46 @@
       <c r="P350" s="20"/>
       <c r="Q350" s="20"/>
       <c r="R350" s="20" t="s">
-        <v>461</v>
-      </c>
-      <c r="S350" s="21" t="s">
-        <v>426</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="S350" s="21"/>
       <c r="T350" s="19"/>
       <c r="U350" s="21"/>
-      <c r="V350" s="20" t="s">
-        <v>345</v>
-      </c>
-      <c r="W350" s="20">
-        <v>6</v>
-      </c>
-      <c r="X350" s="20"/>
-      <c r="Y350" s="20" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="351" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="V350" s="20"/>
+      <c r="W350" s="20"/>
+      <c r="X350" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y350" s="20">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="351" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A351" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B351" s="20" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C351" s="20" t="s">
-        <v>393</v>
-      </c>
-      <c r="D351" s="20"/>
-      <c r="E351" s="20"/>
-      <c r="F351" s="20"/>
-      <c r="G351" s="20"/>
-      <c r="H351" s="20"/>
-      <c r="I351" s="20"/>
-      <c r="J351" s="20"/>
-      <c r="K351" s="20"/>
-      <c r="L351" s="20"/>
-      <c r="M351" s="20"/>
-      <c r="N351" s="20"/>
-      <c r="O351" s="20"/>
-      <c r="P351" s="20"/>
-      <c r="Q351" s="20"/>
-      <c r="R351" s="20" t="s">
-        <v>461</v>
-      </c>
-      <c r="S351" s="21"/>
-      <c r="T351" s="19"/>
-      <c r="U351" s="21"/>
-      <c r="V351" s="20"/>
-      <c r="W351" s="20"/>
-      <c r="X351" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y351" s="20" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="352" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <v>387</v>
+      </c>
+      <c r="R351" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="S351" s="25"/>
+      <c r="T351" s="18"/>
+      <c r="U351" s="25"/>
+      <c r="X351" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y351" s="1">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="352" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A352" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B352" s="20" t="s">
         <v>387</v>
@@ -17522,38 +17485,29 @@
       <c r="C352" s="20" t="s">
         <v>387</v>
       </c>
-      <c r="D352" s="20"/>
-      <c r="E352" s="20"/>
-      <c r="F352" s="20"/>
-      <c r="G352" s="20"/>
-      <c r="H352" s="20"/>
-      <c r="I352" s="20"/>
-      <c r="J352" s="20"/>
-      <c r="K352" s="20"/>
-      <c r="L352" s="20"/>
-      <c r="M352" s="20"/>
-      <c r="N352" s="20"/>
-      <c r="O352" s="20"/>
-      <c r="P352" s="20"/>
-      <c r="Q352" s="20"/>
+      <c r="D352" s="1" t="s">
+        <v>371</v>
+      </c>
       <c r="R352" s="20" t="s">
         <v>369</v>
       </c>
-      <c r="S352" s="21"/>
-      <c r="T352" s="19"/>
-      <c r="U352" s="21"/>
-      <c r="V352" s="20"/>
-      <c r="W352" s="20"/>
-      <c r="X352" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y352" s="20">
-        <v>1701</v>
+      <c r="S352" s="25"/>
+      <c r="T352" s="18" t="s">
+        <v>409</v>
+      </c>
+      <c r="U352" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="X352" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="Y352" s="1">
+        <v>1703</v>
       </c>
     </row>
     <row r="353" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A353" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B353" s="20" t="s">
         <v>387</v>
@@ -17561,22 +17515,29 @@
       <c r="C353" s="20" t="s">
         <v>387</v>
       </c>
+      <c r="D353" s="1" t="s">
+        <v>371</v>
+      </c>
       <c r="R353" s="1" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="S353" s="25"/>
-      <c r="T353" s="18"/>
-      <c r="U353" s="25"/>
+      <c r="T353" s="18" t="s">
+        <v>409</v>
+      </c>
+      <c r="U353" s="21" t="s">
+        <v>400</v>
+      </c>
       <c r="X353" s="1" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="Y353" s="1">
-        <v>1702</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="354" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A354" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B354" s="20" t="s">
         <v>387</v>
@@ -17584,29 +17545,22 @@
       <c r="C354" s="20" t="s">
         <v>387</v>
       </c>
-      <c r="D354" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="R354" s="20" t="s">
-        <v>369</v>
+      <c r="R354" s="1" t="s">
+        <v>379</v>
       </c>
       <c r="S354" s="25"/>
-      <c r="T354" s="18" t="s">
-        <v>409</v>
-      </c>
-      <c r="U354" s="21" t="s">
-        <v>399</v>
-      </c>
+      <c r="T354" s="18"/>
+      <c r="U354" s="25"/>
       <c r="X354" s="1" t="s">
-        <v>264</v>
+        <v>56</v>
       </c>
       <c r="Y354" s="1">
-        <v>1703</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="355" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A355" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B355" s="20" t="s">
         <v>387</v>
@@ -17614,107 +17568,115 @@
       <c r="C355" s="20" t="s">
         <v>387</v>
       </c>
-      <c r="D355" s="1" t="s">
-        <v>371</v>
-      </c>
       <c r="R355" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="S355" s="25"/>
-      <c r="T355" s="18" t="s">
-        <v>409</v>
-      </c>
-      <c r="U355" s="21" t="s">
-        <v>400</v>
-      </c>
+      <c r="T355" s="18"/>
+      <c r="U355" s="25"/>
       <c r="X355" s="1" t="s">
-        <v>47</v>
+        <v>210</v>
       </c>
       <c r="Y355" s="1">
-        <v>1704</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="356" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A356" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B356" s="20" t="s">
         <v>387</v>
       </c>
       <c r="C356" s="20" t="s">
-        <v>387</v>
+        <v>393</v>
+      </c>
+      <c r="D356" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="R356" s="1" t="s">
-        <v>379</v>
+        <v>455</v>
       </c>
       <c r="S356" s="25"/>
       <c r="T356" s="18"/>
       <c r="U356" s="25"/>
       <c r="X356" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="Y356" s="1">
-        <v>1705</v>
+        <v>142</v>
+      </c>
+      <c r="Y356" s="1" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="357" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A357" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B357" s="20" t="s">
         <v>387</v>
       </c>
       <c r="C357" s="20" t="s">
-        <v>387</v>
+        <v>467</v>
+      </c>
+      <c r="G357" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="H357" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="R357" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="S357" s="25"/>
       <c r="T357" s="18"/>
       <c r="U357" s="25"/>
       <c r="X357" s="1" t="s">
-        <v>210</v>
+        <v>264</v>
       </c>
       <c r="Y357" s="1">
-        <v>1706</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="358" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A358" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B358" s="20" t="s">
         <v>387</v>
       </c>
       <c r="C358" s="20" t="s">
-        <v>393</v>
-      </c>
-      <c r="D358" s="1" t="s">
-        <v>373</v>
+        <v>467</v>
+      </c>
+      <c r="G358" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H358" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="R358" s="1" t="s">
-        <v>462</v>
+        <v>382</v>
       </c>
       <c r="S358" s="25"/>
       <c r="T358" s="18"/>
       <c r="U358" s="25"/>
       <c r="X358" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y358" s="1" t="s">
-        <v>476</v>
+        <v>47</v>
+      </c>
+      <c r="Y358" s="1">
+        <v>1707</v>
       </c>
     </row>
     <row r="359" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A359" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B359" s="20" t="s">
         <v>387</v>
       </c>
       <c r="C359" s="20" t="s">
-        <v>475</v>
+        <v>467</v>
+      </c>
+      <c r="D359" s="1" t="s">
+        <v>368</v>
       </c>
       <c r="G359" s="1" t="s">
         <v>185</v>
@@ -17725,25 +17687,34 @@
       <c r="R359" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="S359" s="25"/>
-      <c r="T359" s="18"/>
-      <c r="U359" s="25"/>
-      <c r="X359" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="Y359" s="1">
-        <v>1707</v>
+      <c r="S359" s="21"/>
+      <c r="T359" s="18" t="s">
+        <v>409</v>
+      </c>
+      <c r="U359" s="25" t="s">
+        <v>410</v>
+      </c>
+      <c r="V359" s="20"/>
+      <c r="W359" s="20"/>
+      <c r="X359" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y359" s="20">
+        <v>1708</v>
       </c>
     </row>
     <row r="360" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A360" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B360" s="20" t="s">
         <v>387</v>
       </c>
       <c r="C360" s="20" t="s">
-        <v>475</v>
+        <v>467</v>
+      </c>
+      <c r="D360" s="1" t="s">
+        <v>368</v>
       </c>
       <c r="G360" s="1" t="s">
         <v>27</v>
@@ -17754,25 +17725,31 @@
       <c r="R360" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="S360" s="25"/>
-      <c r="T360" s="18"/>
-      <c r="U360" s="25"/>
-      <c r="X360" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y360" s="1">
-        <v>1707</v>
+      <c r="S360" s="21"/>
+      <c r="T360" s="18" t="s">
+        <v>409</v>
+      </c>
+      <c r="U360" s="25" t="s">
+        <v>410</v>
+      </c>
+      <c r="V360" s="20"/>
+      <c r="W360" s="20"/>
+      <c r="X360" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y360" s="20">
+        <v>1708</v>
       </c>
     </row>
     <row r="361" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A361" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B361" s="20" t="s">
         <v>387</v>
       </c>
       <c r="C361" s="20" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="D361" s="1" t="s">
         <v>368</v>
@@ -17790,13 +17767,13 @@
       <c r="T361" s="18" t="s">
         <v>409</v>
       </c>
-      <c r="U361" s="25" t="s">
-        <v>410</v>
+      <c r="U361" s="21" t="s">
+        <v>411</v>
       </c>
       <c r="V361" s="20"/>
       <c r="W361" s="20"/>
       <c r="X361" s="20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Y361" s="20">
         <v>1708</v>
@@ -17804,13 +17781,13 @@
     </row>
     <row r="362" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A362" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B362" s="20" t="s">
         <v>387</v>
       </c>
       <c r="C362" s="20" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="D362" s="1" t="s">
         <v>368</v>
@@ -17828,13 +17805,13 @@
       <c r="T362" s="18" t="s">
         <v>409</v>
       </c>
-      <c r="U362" s="25" t="s">
-        <v>410</v>
+      <c r="U362" s="21" t="s">
+        <v>411</v>
       </c>
       <c r="V362" s="20"/>
       <c r="W362" s="20"/>
       <c r="X362" s="20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Y362" s="20">
         <v>1708</v>
@@ -17842,130 +17819,128 @@
     </row>
     <row r="363" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A363" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B363" s="20" t="s">
         <v>387</v>
       </c>
       <c r="C363" s="20" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="D363" s="1" t="s">
         <v>368</v>
       </c>
       <c r="G363" s="1" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="H363" s="1" t="s">
         <v>59</v>
       </c>
       <c r="R363" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="S363" s="21"/>
       <c r="T363" s="18" t="s">
         <v>409</v>
       </c>
-      <c r="U363" s="21" t="s">
-        <v>411</v>
+      <c r="U363" s="25" t="s">
+        <v>412</v>
       </c>
       <c r="V363" s="20"/>
       <c r="W363" s="20"/>
       <c r="X363" s="20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Y363" s="20">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="364" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A364" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B364" s="20" t="s">
         <v>387</v>
       </c>
       <c r="C364" s="20" t="s">
-        <v>475</v>
-      </c>
-      <c r="D364" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="G364" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H364" s="1" t="s">
-        <v>59</v>
+        <v>467</v>
+      </c>
+      <c r="D364" s="20" t="s">
+        <v>358</v>
+      </c>
+      <c r="I364" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J364" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="R364" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="S364" s="21"/>
-      <c r="T364" s="18" t="s">
-        <v>409</v>
-      </c>
-      <c r="U364" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="V364" s="20"/>
-      <c r="W364" s="20"/>
-      <c r="X364" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y364" s="20">
-        <v>1708</v>
+        <v>381</v>
+      </c>
+      <c r="S364" s="25" t="s">
+        <v>426</v>
+      </c>
+      <c r="T364" s="18"/>
+      <c r="U364" s="25"/>
+      <c r="V364" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="W364" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="Y364" s="1">
+        <v>1710</v>
       </c>
     </row>
     <row r="365" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A365" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B365" s="20" t="s">
         <v>387</v>
       </c>
       <c r="C365" s="20" t="s">
-        <v>475</v>
-      </c>
-      <c r="D365" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="G365" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H365" s="1" t="s">
-        <v>59</v>
+        <v>467</v>
+      </c>
+      <c r="D365" s="20" t="s">
+        <v>358</v>
+      </c>
+      <c r="I365" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J365" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="R365" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="S365" s="21"/>
-      <c r="T365" s="18" t="s">
-        <v>409</v>
-      </c>
-      <c r="U365" s="25" t="s">
-        <v>412</v>
-      </c>
-      <c r="V365" s="20"/>
-      <c r="W365" s="20"/>
-      <c r="X365" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y365" s="20">
-        <v>1709</v>
+      <c r="S365" s="25" t="s">
+        <v>426</v>
+      </c>
+      <c r="T365" s="18"/>
+      <c r="U365" s="25"/>
+      <c r="V365" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="W365" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="Y365" s="1">
+        <v>1710</v>
       </c>
     </row>
     <row r="366" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A366" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B366" s="20" t="s">
         <v>387</v>
       </c>
       <c r="C366" s="20" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="D366" s="20" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="I366" s="1" t="s">
         <v>12</v>
@@ -17976,9 +17951,7 @@
       <c r="R366" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="S366" s="25" t="s">
-        <v>426</v>
-      </c>
+      <c r="S366" s="25"/>
       <c r="T366" s="18"/>
       <c r="U366" s="25"/>
       <c r="V366" s="20" t="s">
@@ -17993,16 +17966,16 @@
     </row>
     <row r="367" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A367" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B367" s="20" t="s">
         <v>387</v>
       </c>
       <c r="C367" s="20" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="D367" s="20" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="I367" s="1" t="s">
         <v>12</v>
@@ -18013,9 +17986,7 @@
       <c r="R367" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="S367" s="25" t="s">
-        <v>426</v>
-      </c>
+      <c r="S367" s="25"/>
       <c r="T367" s="18"/>
       <c r="U367" s="25"/>
       <c r="V367" s="20" t="s">
@@ -18030,22 +18001,16 @@
     </row>
     <row r="368" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A368" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B368" s="20" t="s">
         <v>387</v>
       </c>
       <c r="C368" s="20" t="s">
-        <v>475</v>
+        <v>386</v>
       </c>
       <c r="D368" s="20" t="s">
-        <v>357</v>
-      </c>
-      <c r="I368" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J368" s="1" t="s">
-        <v>101</v>
+        <v>43</v>
       </c>
       <c r="R368" s="1" t="s">
         <v>381</v>
@@ -18053,54 +18018,42 @@
       <c r="S368" s="25"/>
       <c r="T368" s="18"/>
       <c r="U368" s="25"/>
-      <c r="V368" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="W368" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="Y368" s="1">
-        <v>1710</v>
+      <c r="X368" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y368" s="20" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="369" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A369" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B369" s="20" t="s">
         <v>387</v>
       </c>
       <c r="C369" s="20" t="s">
-        <v>475</v>
+        <v>393</v>
       </c>
       <c r="D369" s="20" t="s">
-        <v>357</v>
-      </c>
-      <c r="I369" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J369" s="1" t="s">
-        <v>101</v>
+        <v>356</v>
       </c>
       <c r="R369" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="S369" s="25"/>
       <c r="T369" s="18"/>
       <c r="U369" s="25"/>
-      <c r="V369" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="W369" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="Y369" s="1">
-        <v>1710</v>
+      <c r="X369" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y369" s="20" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="370" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A370" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B370" s="20" t="s">
         <v>387</v>
@@ -18108,8 +18061,8 @@
       <c r="C370" s="20" t="s">
         <v>386</v>
       </c>
-      <c r="D370" s="20" t="s">
-        <v>43</v>
+      <c r="D370" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="R370" s="1" t="s">
         <v>381</v>
@@ -18117,16 +18070,16 @@
       <c r="S370" s="25"/>
       <c r="T370" s="18"/>
       <c r="U370" s="25"/>
-      <c r="X370" s="20" t="s">
+      <c r="X370" s="1" t="s">
         <v>18</v>
       </c>
       <c r="Y370" s="20" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="371" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A371" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B371" s="20" t="s">
         <v>387</v>
@@ -18134,8 +18087,8 @@
       <c r="C371" s="20" t="s">
         <v>393</v>
       </c>
-      <c r="D371" s="20" t="s">
-        <v>356</v>
+      <c r="D371" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="R371" s="1" t="s">
         <v>381</v>
@@ -18143,16 +18096,16 @@
       <c r="S371" s="25"/>
       <c r="T371" s="18"/>
       <c r="U371" s="25"/>
-      <c r="X371" s="20" t="s">
+      <c r="X371" s="1" t="s">
         <v>33</v>
       </c>
       <c r="Y371" s="20" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="372" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A372" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B372" s="20" t="s">
         <v>387</v>
@@ -18161,7 +18114,7 @@
         <v>386</v>
       </c>
       <c r="D372" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="R372" s="1" t="s">
         <v>381</v>
@@ -18170,15 +18123,15 @@
       <c r="T372" s="18"/>
       <c r="U372" s="25"/>
       <c r="X372" s="1" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="Y372" s="20" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="373" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A373" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B373" s="20" t="s">
         <v>387</v>
@@ -18187,7 +18140,7 @@
         <v>393</v>
       </c>
       <c r="D373" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="R373" s="1" t="s">
         <v>381</v>
@@ -18196,15 +18149,15 @@
       <c r="T373" s="18"/>
       <c r="U373" s="25"/>
       <c r="X373" s="1" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="Y373" s="20" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="374" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A374" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B374" s="20" t="s">
         <v>387</v>
@@ -18213,7 +18166,7 @@
         <v>386</v>
       </c>
       <c r="D374" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="R374" s="1" t="s">
         <v>381</v>
@@ -18222,15 +18175,15 @@
       <c r="T374" s="18"/>
       <c r="U374" s="25"/>
       <c r="X374" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="Y374" s="20" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="375" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A375" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B375" s="20" t="s">
         <v>387</v>
@@ -18239,7 +18192,7 @@
         <v>393</v>
       </c>
       <c r="D375" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="R375" s="1" t="s">
         <v>381</v>
@@ -18248,15 +18201,15 @@
       <c r="T375" s="18"/>
       <c r="U375" s="25"/>
       <c r="X375" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="Y375" s="20" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="376" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A376" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B376" s="20" t="s">
         <v>387</v>
@@ -18264,25 +18217,25 @@
       <c r="C376" s="20" t="s">
         <v>386</v>
       </c>
-      <c r="D376" s="1" t="s">
-        <v>69</v>
+      <c r="D376" s="20" t="s">
+        <v>43</v>
       </c>
       <c r="R376" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="S376" s="25"/>
       <c r="T376" s="18"/>
       <c r="U376" s="25"/>
-      <c r="X376" s="1" t="s">
-        <v>70</v>
+      <c r="X376" s="20" t="s">
+        <v>18</v>
       </c>
       <c r="Y376" s="20" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="377" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A377" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B377" s="20" t="s">
         <v>387</v>
@@ -18290,25 +18243,25 @@
       <c r="C377" s="20" t="s">
         <v>393</v>
       </c>
-      <c r="D377" s="1" t="s">
-        <v>71</v>
+      <c r="D377" s="20" t="s">
+        <v>356</v>
       </c>
       <c r="R377" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="S377" s="25"/>
       <c r="T377" s="18"/>
       <c r="U377" s="25"/>
-      <c r="X377" s="1" t="s">
-        <v>72</v>
+      <c r="X377" s="20" t="s">
+        <v>33</v>
       </c>
       <c r="Y377" s="20" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="378" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A378" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B378" s="20" t="s">
         <v>387</v>
@@ -18316,8 +18269,8 @@
       <c r="C378" s="20" t="s">
         <v>386</v>
       </c>
-      <c r="D378" s="20" t="s">
-        <v>43</v>
+      <c r="D378" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="R378" s="1" t="s">
         <v>382</v>
@@ -18325,16 +18278,16 @@
       <c r="S378" s="25"/>
       <c r="T378" s="18"/>
       <c r="U378" s="25"/>
-      <c r="X378" s="20" t="s">
+      <c r="X378" s="1" t="s">
         <v>18</v>
       </c>
       <c r="Y378" s="20" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="379" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A379" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B379" s="20" t="s">
         <v>387</v>
@@ -18342,8 +18295,8 @@
       <c r="C379" s="20" t="s">
         <v>393</v>
       </c>
-      <c r="D379" s="20" t="s">
-        <v>356</v>
+      <c r="D379" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="R379" s="1" t="s">
         <v>382</v>
@@ -18351,16 +18304,16 @@
       <c r="S379" s="25"/>
       <c r="T379" s="18"/>
       <c r="U379" s="25"/>
-      <c r="X379" s="20" t="s">
+      <c r="X379" s="1" t="s">
         <v>33</v>
       </c>
       <c r="Y379" s="20" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="380" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A380" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B380" s="20" t="s">
         <v>387</v>
@@ -18369,7 +18322,7 @@
         <v>386</v>
       </c>
       <c r="D380" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="R380" s="1" t="s">
         <v>382</v>
@@ -18378,15 +18331,15 @@
       <c r="T380" s="18"/>
       <c r="U380" s="25"/>
       <c r="X380" s="1" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="Y380" s="20" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="381" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A381" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B381" s="20" t="s">
         <v>387</v>
@@ -18395,7 +18348,7 @@
         <v>393</v>
       </c>
       <c r="D381" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="R381" s="1" t="s">
         <v>382</v>
@@ -18404,15 +18357,15 @@
       <c r="T381" s="18"/>
       <c r="U381" s="25"/>
       <c r="X381" s="1" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="Y381" s="20" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="382" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A382" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B382" s="20" t="s">
         <v>387</v>
@@ -18421,7 +18374,7 @@
         <v>386</v>
       </c>
       <c r="D382" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="R382" s="1" t="s">
         <v>382</v>
@@ -18430,15 +18383,15 @@
       <c r="T382" s="18"/>
       <c r="U382" s="25"/>
       <c r="X382" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="Y382" s="20" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="383" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A383" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B383" s="20" t="s">
         <v>387</v>
@@ -18447,7 +18400,7 @@
         <v>393</v>
       </c>
       <c r="D383" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="R383" s="1" t="s">
         <v>382</v>
@@ -18456,278 +18409,10 @@
       <c r="T383" s="18"/>
       <c r="U383" s="25"/>
       <c r="X383" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="Y383" s="20" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="384" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A384" s="7">
-        <v>383</v>
-      </c>
-      <c r="B384" s="20" t="s">
-        <v>387</v>
-      </c>
-      <c r="C384" s="20" t="s">
-        <v>386</v>
-      </c>
-      <c r="D384" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="R384" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="S384" s="25"/>
-      <c r="T384" s="18"/>
-      <c r="U384" s="25"/>
-      <c r="X384" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y384" s="20" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="385" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A385" s="7">
-        <v>384</v>
-      </c>
-      <c r="B385" s="20" t="s">
-        <v>387</v>
-      </c>
-      <c r="C385" s="20" t="s">
-        <v>393</v>
-      </c>
-      <c r="D385" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="R385" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="S385" s="25"/>
-      <c r="T385" s="18"/>
-      <c r="U385" s="25"/>
-      <c r="X385" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y385" s="20" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="386" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A386" s="7">
-        <v>385</v>
-      </c>
-      <c r="B386" s="20" t="s">
-        <v>443</v>
-      </c>
-      <c r="C386" s="20" t="s">
-        <v>393</v>
-      </c>
-      <c r="D386" s="20"/>
-      <c r="E386" s="20"/>
-      <c r="F386" s="20"/>
-      <c r="G386" s="20"/>
-      <c r="H386" s="20"/>
-      <c r="I386" s="20"/>
-      <c r="J386" s="20"/>
-      <c r="K386" s="20"/>
-      <c r="L386" s="20"/>
-      <c r="M386" s="20"/>
-      <c r="N386" s="20"/>
-      <c r="O386" s="20"/>
-      <c r="P386" s="20"/>
-      <c r="Q386" s="20"/>
-      <c r="R386" s="22" t="s">
-        <v>450</v>
-      </c>
-      <c r="S386" s="21"/>
-      <c r="T386" s="19"/>
-      <c r="U386" s="21"/>
-      <c r="V386" s="20"/>
-      <c r="W386" s="20"/>
-      <c r="X386" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y386" s="20" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="387" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A387" s="7">
-        <v>386</v>
-      </c>
-      <c r="B387" s="20" t="s">
-        <v>443</v>
-      </c>
-      <c r="C387" s="20" t="s">
-        <v>443</v>
-      </c>
-      <c r="D387" s="20"/>
-      <c r="E387" s="20"/>
-      <c r="F387" s="20"/>
-      <c r="G387" s="20"/>
-      <c r="H387" s="20"/>
-      <c r="I387" s="20"/>
-      <c r="J387" s="20"/>
-      <c r="K387" s="20"/>
-      <c r="L387" s="20"/>
-      <c r="M387" s="20"/>
-      <c r="N387" s="20"/>
-      <c r="O387" s="20"/>
-      <c r="P387" s="20"/>
-      <c r="Q387" s="20"/>
-      <c r="R387" s="20" t="s">
-        <v>477</v>
-      </c>
-      <c r="S387" s="21"/>
-      <c r="T387" s="18"/>
-      <c r="U387" s="25"/>
-      <c r="V387" s="20" t="s">
-        <v>444</v>
-      </c>
-      <c r="W387" s="20"/>
-      <c r="X387" s="20"/>
-      <c r="Y387" s="20" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="388" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A388" s="7">
-        <v>387</v>
-      </c>
-      <c r="B388" s="20" t="s">
-        <v>443</v>
-      </c>
-      <c r="C388" s="20" t="s">
-        <v>443</v>
-      </c>
-      <c r="D388" s="20"/>
-      <c r="E388" s="20"/>
-      <c r="F388" s="20"/>
-      <c r="G388" s="20"/>
-      <c r="H388" s="20"/>
-      <c r="I388" s="20"/>
-      <c r="J388" s="20"/>
-      <c r="K388" s="20"/>
-      <c r="L388" s="20"/>
-      <c r="M388" s="20"/>
-      <c r="N388" s="20"/>
-      <c r="O388" s="20"/>
-      <c r="P388" s="20"/>
-      <c r="Q388" s="20"/>
-      <c r="R388" s="20" t="s">
-        <v>445</v>
-      </c>
-      <c r="S388" s="21"/>
-      <c r="T388" s="18"/>
-      <c r="U388" s="25"/>
-      <c r="V388" s="20" t="s">
-        <v>444</v>
-      </c>
-      <c r="W388" s="20"/>
-      <c r="X388" s="20"/>
-      <c r="Y388" s="20" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="389" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A389" s="7">
-        <v>388</v>
-      </c>
-      <c r="B389" s="20" t="s">
-        <v>443</v>
-      </c>
-      <c r="C389" s="20" t="s">
-        <v>443</v>
-      </c>
-      <c r="D389" s="20"/>
-      <c r="E389" s="20"/>
-      <c r="F389" s="20"/>
-      <c r="G389" s="20"/>
-      <c r="H389" s="20"/>
-      <c r="I389" s="20"/>
-      <c r="J389" s="20"/>
-      <c r="K389" s="20"/>
-      <c r="L389" s="20"/>
-      <c r="M389" s="20"/>
-      <c r="N389" s="20"/>
-      <c r="O389" s="20"/>
-      <c r="P389" s="20"/>
-      <c r="Q389" s="20"/>
-      <c r="R389" s="20" t="s">
-        <v>390</v>
-      </c>
-      <c r="S389" s="21"/>
-      <c r="T389" s="18"/>
-      <c r="U389" s="25"/>
-      <c r="V389" s="20" t="s">
-        <v>446</v>
-      </c>
-      <c r="W389" s="20"/>
-      <c r="X389" s="20"/>
-      <c r="Y389" s="20" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="390" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A390" s="7">
-        <v>389</v>
-      </c>
-      <c r="B390" s="20" t="s">
-        <v>443</v>
-      </c>
-      <c r="C390" s="20" t="s">
-        <v>443</v>
-      </c>
-      <c r="R390" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="V390" s="20" t="s">
-        <v>446</v>
-      </c>
-      <c r="Y390" s="20" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="391" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A391" s="7">
-        <v>390</v>
-      </c>
-      <c r="B391" s="20" t="s">
-        <v>443</v>
-      </c>
-      <c r="C391" s="20" t="s">
-        <v>393</v>
-      </c>
-      <c r="R391" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="X391" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y391" s="20" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="392" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A392" s="7">
-        <v>391</v>
-      </c>
-      <c r="B392" s="20" t="s">
-        <v>443</v>
-      </c>
-      <c r="C392" s="20" t="s">
-        <v>393</v>
-      </c>
-      <c r="R392" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="X392" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y392" s="20" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>
@@ -18763,7 +18448,7 @@
         <v>89</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.2">
@@ -18833,7 +18518,7 @@
         <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -18847,7 +18532,7 @@
         <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="E7" t="s">
         <v>90</v>
@@ -18987,7 +18672,7 @@
         <v>224</v>
       </c>
       <c r="C17" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="D17" t="s">
         <v>166</v>
@@ -19079,7 +18764,7 @@
         <v>324</v>
       </c>
       <c r="B24" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="C24" t="s">
         <v>329</v>
@@ -19090,7 +18775,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="B25" t="s">
         <v>0</v>
@@ -19104,10 +18789,10 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="B26" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="C26" t="s">
         <v>159</v>
@@ -19428,13 +19113,13 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="B78" t="s">
         <v>444</v>
       </c>
-      <c r="B78" t="s">
-        <v>447</v>
-      </c>
       <c r="C78" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -19482,7 +19167,7 @@
         <v>423</v>
       </c>
       <c r="C84" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="D84" t="s">
         <v>119</v>
@@ -19626,13 +19311,13 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" s="18" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="B96" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="C96" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="D96" t="s">
         <v>119</v>
